--- a/data/trans_orig/IP07_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07_R2-Edad-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2007 (tasa de respuesta: 99,81%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2007 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6698</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1070</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4033</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3682</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2664</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6040</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118716</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114682</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120683</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>105101</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>102138</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>102489</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118716</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>115340</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>120719</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>338</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219782</t>
+          <t>219528</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>226213</t>
+          <t>226217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8801</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4819</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14706</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1970</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8801</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4787</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15554</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>243456</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>237551</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>247438</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>376</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>251235</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>247429</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>252591</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>247996</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>252584</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>243456</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>236703</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>247470</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>488929</t>
+          <t>488679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>498838</t>
+          <t>498886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252257</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252257</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252257</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252257</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252257</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252257</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13435</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6788</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6075</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7924</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4356</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13580</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>133591</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>128080</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>137075</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>124848</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120760</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126864</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>121473</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>126814</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>133591</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>127935</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>137159</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>252346</t>
+          <t>252333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>262900</t>
+          <t>262575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1757,67 +1757,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>6024</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10759</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>5905</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2716</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11156</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10878</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10713</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>198714</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>193979</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202043</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>188192</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>182941</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>191381</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>183219</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>190886</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>198714</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>194025</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>201469</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,06%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380260</t>
+          <t>379779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>391526</t>
+          <t>391601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204738</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204738</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204738</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204738</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204738</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,74 +2095,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18490</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35297</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11645</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7265</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18649</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6868</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18628</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>25414</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>18030</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>33821</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>56</t>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>28607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>694476</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>684593</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>701400</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>669376</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>662372</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>673756</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>662393</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>674153</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>97,26%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>694476</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>686069</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>701860</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,47%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1353957</t>
+          <t>1353306</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1373378</t>
+          <t>1372304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>719890</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>719890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2512</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10282</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4755</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9235</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9967</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9173</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>140157</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>134993</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>142763</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>142006</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>137526</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>144717</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>136794</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>144677</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,76%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>140157</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>136102</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>142981</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276345</t>
+          <t>276505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>286146</t>
+          <t>286175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>145275</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>145275</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>145275</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>145275</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>145275</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>145275</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5449</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4826</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9228</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9971</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5381</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>264048</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>260596</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>265395</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>229939</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>225537</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>232804</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>224794</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>232562</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>264048</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>260664</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>265399</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>489049</t>
+          <t>488675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>497503</t>
+          <t>497428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>266045</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>266045</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>266045</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234765</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234765</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234765</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>266045</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>266045</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>266045</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4887</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2229</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9250</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3513</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7861</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8199</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9707</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>153684</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149321</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>156342</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153530</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149182</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>155728</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148844</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>155716</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,76%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,78%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>99,16%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>153684</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>148864</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>156496</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>439</t>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>301474</t>
+          <t>301783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311315</t>
+          <t>310931</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6724</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12744</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3526</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8776</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7819</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6724</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3397</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>11647</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16609</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173231</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>167211</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>176643</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>167075</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>161825</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>169262</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>162782</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>169302</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,93%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>173231</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>168308</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>176558</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333947</t>
+          <t>333303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>344612</t>
+          <t>344522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170601</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170601</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170601</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12486</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26716</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>16619</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10563</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24280</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10857</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24748</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>18726</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13095</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26308</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26198</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46783</t>
+          <t>46163</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>731120</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>723130</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>737360</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>998</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>692551</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>698607</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>684422</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>698313</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>731120</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>723538</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>736751</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1412233</t>
+          <t>1412853</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1432818</t>
+          <t>1431978</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749846</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>709170</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2016 (tasa de respuesta: 99,48%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2016 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8904</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2362</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5529</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4542</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9484</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118854</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114492</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121490</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,32%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>128567</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>125400</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>130346</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>125078</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>130354</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118854</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>113912</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>121403</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>242306</t>
+          <t>242616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250611</t>
+          <t>250702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>123396</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>123396</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>123396</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>130929</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>130929</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>130929</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>123396</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>123396</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>123396</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2540</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6675</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4833</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10185</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1836</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9864</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,32%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2540</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5660</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>254875</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>250740</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>256760</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>321</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>203251</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>197899</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>206278</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>198220</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>206248</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>254875</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>251755</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>256785</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452512</t>
+          <t>452909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>461603</t>
+          <t>461628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>257415</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>208084</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>208084</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>208084</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>257415</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10345</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2747</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6682</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6730</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4601</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9612</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>183971</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>178227</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>186636</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>185477</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>181542</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>187252</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>181494</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>187579</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,54%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>183971</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>178960</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>186477</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>364157</t>
+          <t>364302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372906</t>
+          <t>373108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188224</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188224</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188224</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8399</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>3456</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1196</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7615</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7522</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3816</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8016</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>168825</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>164242</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>171348</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>169079</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>164920</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>171339</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>165013</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>171271</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>168825</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>164625</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>171305</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332216</t>
+          <t>331533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341558</t>
+          <t>341414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>172641</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>172641</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>172641</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172535</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172641</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172641</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172641</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23187</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13398</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8737</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>21336</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8496</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20805</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9417</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>22821</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>37817</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>726525</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>718837</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>732440</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1034</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>686375</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>678437</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>691036</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>678968</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>691277</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,09%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>726525</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>719203</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>732607</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1403464</t>
+          <t>1403980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1420876</t>
+          <t>1420256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>742024</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1054</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>699773</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>742024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores cuya salud general, percibida por el adulto, es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general, percibida por el/la adulto/a, es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7544</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4929</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4761</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4504</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>9743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46780</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42993</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49048</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56178</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52582</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>50784</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47329</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56940</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52448</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60018</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,67%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>85,36%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>113118</t>
+          <t>97565</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107553</t>
+          <t>92884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116278</t>
+          <t>100194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2815</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7125</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2745</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6847</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,17 +6982,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>10878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>154707</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>150397</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>156530</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>156554</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>152452</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>158665</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>179241</t>
+          <t>142969</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175040</t>
+          <t>137951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>181580</t>
+          <t>144640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,17 +7095,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>335795</t>
+          <t>297675</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330111</t>
+          <t>292161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>339028</t>
+          <t>300596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12007</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11413</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>11852</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18757</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>194918</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>188119</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>198029</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>167897</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>162475</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>171157</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>207003</t>
+          <t>169519</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200720</t>
+          <t>163666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>210213</t>
+          <t>172493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>374900</t>
+          <t>364437</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>367621</t>
+          <t>357323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>380162</t>
+          <t>369285</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10891</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11076</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34087</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>6889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37989</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>287294</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>281754</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>290434</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>264382</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>241371</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>271397</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>300118</t>
+          <t>250267</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294434</t>
+          <t>244598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303288</t>
+          <t>253795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>564500</t>
+          <t>537560</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>542951</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>572417</t>
+          <t>542309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10764</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25332</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12880</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>44185</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27555</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>24678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62247</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>683698</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>675497</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>690065</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>645011</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>621970</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>653275</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>743303</t>
+          <t>613538</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>734417</t>
+          <t>605552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>750007</t>
+          <t>619734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1388314</t>
+          <t>1297237</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1365880</t>
+          <t>1286599</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1400058</t>
+          <t>1305830</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
